--- a/generator/pyhton/v_6/samples/samples_/fault_row.xlsx
+++ b/generator/pyhton/v_6/samples/samples_/fault_row.xlsx
@@ -249,7 +249,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -258,7 +258,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -270,10 +270,6 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -334,16 +330,12 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -535,7 +527,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:U47"/>
+  <dimension ref="A2:X54"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.79"/>
@@ -783,50 +775,50 @@
       <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B16" s="7" t="n">
+      <c r="B16" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7" t="n">
+      <c r="C16" s="6"/>
+      <c r="D16" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7" t="n">
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7" t="n">
+      <c r="H16" s="6"/>
+      <c r="I16" s="6" t="n">
         <v>75</v>
       </c>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="8" t="s">
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="N16" s="8" t="n">
+      <c r="N16" s="7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6"/>
+      <c r="A17" s="5"/>
       <c r="B17" s="4" t="s">
         <v>11</v>
       </c>
@@ -861,7 +853,7 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6"/>
+      <c r="A18" s="5"/>
       <c r="B18" s="4" t="n">
         <f aca="false">(N17/100)*B16</f>
         <v>19</v>
@@ -901,7 +893,7 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C20" s="4" t="s">
@@ -922,8 +914,8 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9"/>
-      <c r="B21" s="10" t="s">
+      <c r="A21" s="8"/>
+      <c r="B21" s="9" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="1" t="n">
@@ -943,8 +935,8 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="9"/>
-      <c r="B22" s="10" t="s">
+      <c r="A22" s="8"/>
+      <c r="B22" s="9" t="s">
         <v>16</v>
       </c>
       <c r="C22" s="1" t="n">
@@ -964,55 +956,55 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9"/>
-      <c r="B23" s="10" t="s">
+      <c r="A23" s="8"/>
+      <c r="B23" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="11" t="n">
+      <c r="C23" s="10" t="n">
         <f aca="false">C21/((SQRT(3)*C22))</f>
         <v>57735.0269189626</v>
       </c>
-      <c r="D23" s="11" t="n">
+      <c r="D23" s="10" t="n">
         <f aca="false">D21/((SQRT(3)*D22))</f>
         <v>1732.05080756888</v>
       </c>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11" t="n">
+      <c r="E23" s="10"/>
+      <c r="F23" s="10" t="n">
         <f aca="false">F21/((SQRT(3)*F22))</f>
         <v>1732.05080756888</v>
       </c>
-      <c r="G23" s="11" t="n">
+      <c r="G23" s="10" t="n">
         <f aca="false">G21/((SQRT(3)*G22))</f>
         <v>1732.05080756888</v>
       </c>
-      <c r="H23" s="11" t="n">
+      <c r="H23" s="10" t="n">
         <f aca="false">H21/((SQRT(3)*H22))</f>
         <v>1732.05080756888</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9"/>
-      <c r="B24" s="10" t="s">
+      <c r="A24" s="8"/>
+      <c r="B24" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="12" t="n">
+      <c r="C24" s="11" t="n">
         <f aca="false">(C22*C22)/C21</f>
         <v>0.15</v>
       </c>
-      <c r="D24" s="12" t="n">
+      <c r="D24" s="11" t="n">
         <f aca="false">(D22*D22)/D21</f>
         <v>166.666666666667</v>
       </c>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12" t="n">
+      <c r="E24" s="11"/>
+      <c r="F24" s="11" t="n">
         <f aca="false">(F22*F22)/F21</f>
         <v>166.666666666667</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="G24" s="11" t="n">
         <f aca="false">(G22*G22)/G21</f>
         <v>166.666666666667</v>
       </c>
-      <c r="H24" s="12" t="n">
+      <c r="H24" s="11" t="n">
         <f aca="false">(H22*H22)/H21</f>
         <v>166.666666666667</v>
       </c>
@@ -1047,18 +1039,18 @@
       <c r="D27" s="4" t="n">
         <v>3.41</v>
       </c>
-      <c r="E27" s="13" t="str">
+      <c r="E27" s="12" t="str">
         <f aca="false">COMPLEX(C27*COS(RADIANS(D27)),C27*SIN(RADIANS(D27)),"j")</f>
         <v>1,01819405104099+0,0606702103567876j</v>
       </c>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="10" t="n">
+      <c r="B28" s="9" t="n">
         <v>501270</v>
       </c>
       <c r="C28" s="4" t="n">
@@ -1068,43 +1060,43 @@
       <c r="D28" s="4" t="n">
         <v>-40</v>
       </c>
-      <c r="E28" s="13" t="str">
+      <c r="E28" s="12" t="str">
         <f aca="false">COMPLEX(C28*COS(RADIANS(D28)),C28*SIN(RADIANS(D28)),"j")</f>
         <v>0,7679901960045-0,644420290215143j</v>
       </c>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
     </row>
     <row r="31" customFormat="false" ht="19.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="15" t="s">
+      <c r="A31" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="B31" s="15"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="15"/>
-      <c r="K31" s="15"/>
-      <c r="L31" s="15"/>
-      <c r="M31" s="15"/>
-      <c r="N31" s="15"/>
-      <c r="O31" s="15"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="14"/>
+      <c r="N31" s="14"/>
+      <c r="O31" s="14"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="3" t="s">
@@ -1133,7 +1125,7 @@
       <c r="R32" s="3"/>
       <c r="S32" s="3"/>
       <c r="T32" s="3"/>
-      <c r="U32" s="10" t="s">
+      <c r="U32" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1176,7 +1168,7 @@
       <c r="O33" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="Q33" s="16" t="s">
+      <c r="Q33" s="15" t="s">
         <v>36</v>
       </c>
       <c r="R33" s="4" t="s">
@@ -1193,43 +1185,43 @@
       <c r="A34" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="17" t="n">
+      <c r="B34" s="16" t="n">
         <f aca="false">IMABS(IMSUB(E27,IMPRODUCT(E34,IMSUM(B10,D10))))</f>
         <v>0.0458776461793521</v>
       </c>
-      <c r="C34" s="17" t="n">
+      <c r="C34" s="16" t="n">
         <f aca="false">B34*(F22/(SQRT(3)))</f>
         <v>13243.7356857177</v>
       </c>
-      <c r="D34" s="17" t="n">
+      <c r="D34" s="16" t="n">
         <f aca="false">IMABS(IMDIV(E27,IMSUM(B10,D10,IMPRODUCT(B18,G10) )))</f>
         <v>1.4669124083737</v>
       </c>
-      <c r="E34" s="17" t="str">
+      <c r="E34" s="16" t="str">
         <f aca="false">IMDIV(E27,IMSUM(B10,D10,IMPRODUCT(B18,G10)))</f>
         <v>0,123826175770252-1,46167680833857j</v>
       </c>
-      <c r="F34" s="18" t="n">
+      <c r="F34" s="17" t="n">
         <f aca="false">D34*F23</f>
         <v>2540.76682155647</v>
       </c>
-      <c r="G34" s="17" t="n">
+      <c r="G34" s="16" t="n">
         <f aca="false">IMABS(IMSUB(E28,IMPRODUCT(J34,IMSUM(I10,L10))))</f>
         <v>0.301169391927739</v>
       </c>
-      <c r="H34" s="17" t="n">
+      <c r="H34" s="16" t="n">
         <f aca="false">G34*(H22/SQRT(3))</f>
         <v>86940.114750578</v>
       </c>
-      <c r="I34" s="17" t="n">
+      <c r="I34" s="16" t="n">
         <f aca="false">IMABS(IMDIV(C28,IMSUM(I10,L10,IMPRODUCT(C18,G10) )))</f>
         <v>1.06996944852949</v>
       </c>
-      <c r="J34" s="17" t="str">
+      <c r="J34" s="16" t="str">
         <f aca="false">IMDIV(E28,IMSUM(L10,I10,IMPRODUCT(C18,G10)))</f>
         <v>-0,622475839997205-0,870263436785832j</v>
       </c>
-      <c r="K34" s="17" t="n">
+      <c r="K34" s="16" t="n">
         <f aca="false">I34*F23</f>
         <v>1853.24144739953</v>
       </c>
@@ -1239,23 +1231,23 @@
       <c r="M34" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N34" s="17" t="n">
+      <c r="N34" s="16" t="n">
         <f aca="false">IMABS(IMSUM(E34,J34))</f>
         <v>2.38465863269033</v>
       </c>
-      <c r="O34" s="19" t="n">
+      <c r="O34" s="18" t="n">
         <f aca="false">N34*F23</f>
         <v>4130.34991052738</v>
       </c>
-      <c r="Q34" s="17" t="n">
+      <c r="Q34" s="16" t="n">
         <f aca="false">IMABS(IMPRODUCT(D24,IMPRODUCT(N17,G10)))</f>
         <v>52.1249552432531</v>
       </c>
-      <c r="R34" s="17" t="n">
+      <c r="R34" s="16" t="n">
         <f aca="false">C34/F34</f>
         <v>5.21249552432545</v>
       </c>
-      <c r="S34" s="17" t="n">
+      <c r="S34" s="16" t="n">
         <f aca="false">H34/K34</f>
         <v>46.9124597189278</v>
       </c>
@@ -1263,7 +1255,7 @@
         <f aca="false">(R34/Q34)*100</f>
         <v>10.0000000000003</v>
       </c>
-      <c r="U34" s="10" t="s">
+      <c r="U34" s="9" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1271,43 +1263,43 @@
       <c r="A35" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="20" t="n">
+      <c r="B35" s="19" t="n">
         <f aca="false">IMABS(IMSUB(E27,IMPRODUCT(E35,IMSUM(B10,D10))))</f>
         <v>0.107448751713412</v>
       </c>
-      <c r="C35" s="17" t="n">
+      <c r="C35" s="16" t="n">
         <f aca="false">B35*(F22/(SQRT(3)))</f>
         <v>31017.7828629139</v>
       </c>
-      <c r="D35" s="17" t="n">
+      <c r="D35" s="16" t="n">
         <f aca="false">IMABS(IMDIV(E27,IMSUM(B10,D10,IMPRODUCT(D18,G10) )))</f>
         <v>1.3742458062167</v>
       </c>
-      <c r="E35" s="17" t="str">
+      <c r="E35" s="16" t="str">
         <f aca="false">IMDIV(E27,IMSUM(B10,D10,IMPRODUCT(D18,G10)))</f>
         <v>0,118934468200217-1,36908952526054j</v>
       </c>
-      <c r="F35" s="18" t="n">
+      <c r="F35" s="17" t="n">
         <f aca="false">D35*F23</f>
         <v>2380.26355845579</v>
       </c>
-      <c r="G35" s="17" t="n">
+      <c r="G35" s="16" t="n">
         <f aca="false">IMABS(IMSUB(E28,IMPRODUCT(J35,IMSUM(I10,L10))))</f>
         <v>0.264200041295128</v>
       </c>
-      <c r="H35" s="17" t="n">
+      <c r="H35" s="16" t="n">
         <f aca="false">G35*(H22/SQRT(3))</f>
         <v>76267.9824808262</v>
       </c>
-      <c r="I35" s="17" t="n">
+      <c r="I35" s="16" t="n">
         <f aca="false">IMABS(IMDIV(C28,IMSUM(I10,L10,IMPRODUCT(F18,G10) )))</f>
         <v>1.12635339471885</v>
       </c>
-      <c r="J35" s="17" t="str">
+      <c r="J35" s="16" t="str">
         <f aca="false">IMDIV(E28,IMSUM(L10,I10,IMPRODUCT(F18,G10)))</f>
         <v>-0,654391443997033-0,916757224033806j</v>
       </c>
-      <c r="K35" s="17" t="n">
+      <c r="K35" s="16" t="n">
         <f aca="false">I35*F23</f>
         <v>1950.90130693074</v>
       </c>
@@ -1317,23 +1309,23 @@
       <c r="M35" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N35" s="17" t="n">
+      <c r="N35" s="16" t="n">
         <f aca="false">IMABS(IMSUM(E35,J35))</f>
         <v>2.34772433096158</v>
       </c>
-      <c r="O35" s="19" t="n">
+      <c r="O35" s="18" t="n">
         <f aca="false">N35*F23</f>
         <v>4066.37782339111</v>
       </c>
-      <c r="Q35" s="17" t="n">
+      <c r="Q35" s="16" t="n">
         <f aca="false">IMABS(IMPRODUCT(D24,IMPRODUCT(N17,G10)))</f>
         <v>52.1249552432531</v>
       </c>
-      <c r="R35" s="17" t="n">
+      <c r="R35" s="16" t="n">
         <f aca="false">C35/F35</f>
         <v>13.0312388108134</v>
       </c>
-      <c r="S35" s="17" t="n">
+      <c r="S35" s="16" t="n">
         <f aca="false">H35/K35</f>
         <v>39.0937164324397</v>
       </c>
@@ -1341,7 +1333,7 @@
         <f aca="false">(R35/Q35)*100</f>
         <v>25.0000000000003</v>
       </c>
-      <c r="U35" s="10" t="s">
+      <c r="U35" s="9" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1349,43 +1341,43 @@
       <c r="A36" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="20" t="n">
+      <c r="B36" s="19" t="n">
         <f aca="false">IMABS(IMSUB(E27,IMPRODUCT(E36,IMSUM(B10,D10))))</f>
         <v>0.194425658877859</v>
       </c>
-      <c r="C36" s="17" t="n">
+      <c r="C36" s="16" t="n">
         <f aca="false">B36*(F22/(SQRT(3)))</f>
         <v>56125.853245251</v>
       </c>
-      <c r="D36" s="17" t="n">
+      <c r="D36" s="16" t="n">
         <f aca="false">IMABS(IMDIV(E27,IMSUM(B10,D10,IMPRODUCT(G18,G10) )))</f>
         <v>1.24333062075243</v>
       </c>
-      <c r="E36" s="17" t="str">
+      <c r="E36" s="16" t="str">
         <f aca="false">IMDIV(E27,IMSUM(B10,D10,IMPRODUCT(G18,G10)))</f>
         <v>0,111348962412485-1,23833454327588j</v>
       </c>
-      <c r="F36" s="18" t="n">
+      <c r="F36" s="17" t="n">
         <f aca="false">D36*F23</f>
         <v>2153.51180574936</v>
       </c>
-      <c r="G36" s="17" t="n">
+      <c r="G36" s="16" t="n">
         <f aca="false">IMABS(IMSUB(E28,IMPRODUCT(J36,IMSUM(I10,L10))))</f>
         <v>0.193091753682451</v>
       </c>
-      <c r="H36" s="17" t="n">
+      <c r="H36" s="16" t="n">
         <f aca="false">G36*(H22/SQRT(3))</f>
         <v>55740.7879834301</v>
       </c>
-      <c r="I36" s="17" t="n">
+      <c r="I36" s="16" t="n">
         <f aca="false">IMABS(IMDIV(C28,IMSUM(I10,L10,IMPRODUCT(H18,G10) )))</f>
         <v>1.23480044431273</v>
       </c>
-      <c r="J36" s="17" t="str">
+      <c r="J36" s="16" t="str">
         <f aca="false">IMDIV(E28,IMSUM(L10,I10,IMPRODUCT(H18,G10)))</f>
         <v>-0,71552531556579-1,00635762036136j</v>
       </c>
-      <c r="K36" s="17" t="n">
+      <c r="K36" s="16" t="n">
         <f aca="false">I36*F23</f>
         <v>2138.73710675827</v>
       </c>
@@ -1395,23 +1387,23 @@
       <c r="M36" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N36" s="17" t="n">
+      <c r="N36" s="16" t="n">
         <f aca="false">IMABS(IMSUM(E36,J36))</f>
         <v>2.32457995672424</v>
       </c>
-      <c r="O36" s="19" t="n">
+      <c r="O36" s="18" t="n">
         <f aca="false">N36*F23</f>
         <v>4026.29059130264</v>
       </c>
-      <c r="Q36" s="17" t="n">
+      <c r="Q36" s="16" t="n">
         <f aca="false">IMABS(IMPRODUCT(D24,IMPRODUCT(N17,G10)))</f>
         <v>52.1249552432531</v>
       </c>
-      <c r="R36" s="17" t="n">
+      <c r="R36" s="16" t="n">
         <f aca="false">C36/F36</f>
         <v>26.0624776216265</v>
       </c>
-      <c r="S36" s="17" t="n">
+      <c r="S36" s="16" t="n">
         <f aca="false">H36/K36</f>
         <v>26.0624776216268</v>
       </c>
@@ -1419,7 +1411,7 @@
         <f aca="false">(R36/Q36)*100</f>
         <v>49.9999999999998</v>
       </c>
-      <c r="U36" s="10" t="s">
+      <c r="U36" s="9" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1427,43 +1419,43 @@
       <c r="A37" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B37" s="20" t="n">
+      <c r="B37" s="19" t="n">
         <f aca="false">IMABS(IMSUB(E27,IMPRODUCT(E37,IMSUM(B10,D10))))</f>
         <v>0.266270657138407</v>
       </c>
-      <c r="C37" s="17" t="n">
+      <c r="C37" s="16" t="n">
         <f aca="false">B37*(F22/(SQRT(3)))</f>
         <v>76865.7177880788</v>
       </c>
-      <c r="D37" s="17" t="n">
+      <c r="D37" s="16" t="n">
         <f aca="false">IMABS(IMDIV(E27,IMSUM(B10,D10,IMPRODUCT(I18,G10) )))</f>
         <v>1.13518096784413</v>
       </c>
-      <c r="E37" s="17" t="str">
+      <c r="E37" s="16" t="str">
         <f aca="false">IMDIV(E27,IMSUM(B10,D10,IMPRODUCT(I18,G10)))</f>
         <v>0,104486819931915-1,13036203679001j</v>
       </c>
-      <c r="F37" s="18" t="n">
+      <c r="F37" s="17" t="n">
         <f aca="false">D37*F23</f>
         <v>1966.19111209125</v>
       </c>
-      <c r="G37" s="17" t="n">
+      <c r="G37" s="16" t="n">
         <f aca="false">IMABS(IMSUB(E28,IMPRODUCT(J37,IMSUM(I10,L10))))</f>
         <v>0.106831312050452</v>
       </c>
-      <c r="H37" s="17" t="n">
+      <c r="H37" s="16" t="n">
         <f aca="false">G37*(H22/SQRT(3))</f>
         <v>30839.5433851047</v>
       </c>
-      <c r="I37" s="17" t="n">
+      <c r="I37" s="16" t="n">
         <f aca="false">IMABS(IMDIV(C28,IMSUM(I10,L10,IMPRODUCT(K18,G10) )))</f>
         <v>1.36634888927832</v>
       </c>
-      <c r="J37" s="17" t="str">
+      <c r="J37" s="16" t="str">
         <f aca="false">IMDIV(E28,IMSUM(L10,I10,IMPRODUCT(K18,G10)))</f>
         <v>-0,789236800117179-1,11535400683948j</v>
       </c>
-      <c r="K37" s="17" t="n">
+      <c r="K37" s="16" t="n">
         <f aca="false">I37*F23</f>
         <v>2366.58569709535</v>
       </c>
@@ -1473,23 +1465,23 @@
       <c r="M37" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N37" s="17" t="n">
+      <c r="N37" s="16" t="n">
         <f aca="false">IMABS(IMSUM(E37,J37))</f>
         <v>2.34779110739832</v>
       </c>
-      <c r="O37" s="19" t="n">
+      <c r="O37" s="18" t="n">
         <f aca="false">N37*F23</f>
         <v>4066.49348357228</v>
       </c>
-      <c r="Q37" s="17" t="n">
+      <c r="Q37" s="16" t="n">
         <f aca="false">IMABS(IMPRODUCT(D24,IMPRODUCT(N17,G10)))</f>
         <v>52.1249552432531</v>
       </c>
-      <c r="R37" s="17" t="n">
+      <c r="R37" s="16" t="n">
         <f aca="false">C37/F37</f>
         <v>39.0937164324398</v>
       </c>
-      <c r="S37" s="17" t="n">
+      <c r="S37" s="16" t="n">
         <f aca="false">H37/K37</f>
         <v>13.0312388108133</v>
       </c>
@@ -1497,12 +1489,12 @@
         <f aca="false">(R37/Q37)*100</f>
         <v>74.9999999999999</v>
       </c>
-      <c r="U37" s="10" t="s">
+      <c r="U37" s="9" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="T38" s="21" t="n">
+      <c r="T38" s="20" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1512,27 +1504,27 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
     </row>
     <row r="42" customFormat="false" ht="18.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="23" t="s">
+      <c r="A42" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="B42" s="23"/>
-      <c r="C42" s="23"/>
-      <c r="D42" s="23"/>
-      <c r="E42" s="23"/>
-      <c r="F42" s="23"/>
-      <c r="G42" s="23"/>
-      <c r="H42" s="23"/>
-      <c r="I42" s="23"/>
-      <c r="J42" s="23"/>
-      <c r="K42" s="23"/>
-      <c r="L42" s="23"/>
-      <c r="M42" s="23"/>
-      <c r="N42" s="23"/>
-      <c r="O42" s="23"/>
+      <c r="B42" s="14"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
+      <c r="H42" s="14"/>
+      <c r="I42" s="14"/>
+      <c r="J42" s="14"/>
+      <c r="K42" s="14"/>
+      <c r="L42" s="14"/>
+      <c r="M42" s="14"/>
+      <c r="N42" s="14"/>
+      <c r="O42" s="14"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="3" t="s">
@@ -1612,6 +1604,11 @@
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="X54" s="0" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
